--- a/artfynd/S 987-2022 artfynd.xlsx
+++ b/artfynd/S 987-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94952591</v>
+        <v>135855635</v>
       </c>
       <c r="B2" t="n">
-        <v>97983</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kosta 312, Sm</t>
+          <t>Målerås, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530470</v>
+        <v>531080</v>
       </c>
       <c r="R2" t="n">
-        <v>6308161</v>
+        <v>6308459</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-20</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-10-15</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,42 +780,28 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>produktionsskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Petersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Petersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Inventering av tall- och granproduktionsskog i södra Småland</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94952591</t>
+          <t>https://artportalen.se/Sighting/135855635</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94952600</v>
+        <v>94952591</v>
       </c>
       <c r="B3" t="n">
         <v>97983</v>
@@ -827,14 +832,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kosta 311, Sm</t>
+          <t>Kosta 312, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530488</v>
+        <v>530470</v>
       </c>
       <c r="R3" t="n">
-        <v>6308164</v>
+        <v>6308161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,16 +911,16 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94952600</t>
+          <t>https://artportalen.se/Sighting/94952591</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88221374</v>
+        <v>94952600</v>
       </c>
       <c r="B4" t="n">
-        <v>89823</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,48 +928,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2979</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Giljeskruv, Sm</t>
+          <t>Kosta 311, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530411</v>
+        <v>530488</v>
       </c>
       <c r="R4" t="n">
-        <v>6306455</v>
+        <v>6308164</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,12 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2016-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2016-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,34 +996,47 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>produktionsskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Lisa Petersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Backman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Lisa Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av tall- och granproduktionsskog i södra Småland</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88221374</t>
+          <t>https://artportalen.se/Sighting/94952600</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74553701</v>
+        <v>88221374</v>
       </c>
       <c r="B5" t="n">
-        <v>107608</v>
+        <v>89823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,37 +1044,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>2979</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skruvagöl 500 m N, Sm</t>
+          <t>Giljeskruv, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530403</v>
+        <v>530411</v>
       </c>
       <c r="R5" t="n">
-        <v>6306528</v>
+        <v>6306455</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,17 +1109,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3313. SOM: Lathraea squamaria. LEG: Bengt-Erik Eriksson</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,42 +1123,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Hassel intill inäga</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74553701</t>
+          <t>https://artportalen.se/Sighting/88221374</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2400167</v>
+        <v>74553701</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>107608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,51 +1158,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219686</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Målerås, Sm</t>
+          <t>Skruvagöl 500 m N, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530484</v>
+        <v>530403</v>
       </c>
       <c r="R6" t="n">
-        <v>6306439</v>
+        <v>6306528</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,12 +1212,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-06-29</t>
+          <t>1983-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F1g 3313. SOM: Lathraea squamaria. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,71 +1236,89 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Hassel intill inäga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2400167</t>
+          <t>https://artportalen.se/Sighting/74553701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74552902</v>
+        <v>2400167</v>
       </c>
       <c r="B7" t="n">
-        <v>102240</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skruvagöl 500 m N, Sm</t>
+          <t>Målerås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530403</v>
+        <v>530484</v>
       </c>
       <c r="R7" t="n">
-        <v>6306528</v>
+        <v>6306439</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,17 +1342,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3313. SOM: Lathyrus vernus. LEG: Bengt-Erik Eriksson</t>
+          <t>2005-06-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,37 +1361,33 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Hassel intill inäga</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Jörg Adelmann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74552902</t>
+          <t>https://artportalen.se/Sighting/2400167</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75062708</v>
+        <v>74552902</v>
       </c>
       <c r="B8" t="n">
-        <v>101793</v>
+        <v>102240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,34 +1395,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222929</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backruta</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thalictrum simplex</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skruvagöl 450 m N, Sm</t>
+          <t>Skruvagöl 500 m N, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530404</v>
+        <v>530403</v>
       </c>
       <c r="R8" t="n">
-        <v>6306428</v>
+        <v>6306528</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1454,7 +1459,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3213. SOM: Thalictrum simplex. LEG: Bengt-Erik Eriksson. KOM: Det. ThK</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3313. SOM: Lathyrus vernus. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,7 +1473,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Åkerkant</t>
+          <t>Hassel intill inäga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1489,58 +1494,54 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75062708</t>
+          <t>https://artportalen.se/Sighting/74552902</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88236870</v>
+        <v>75062708</v>
       </c>
       <c r="B9" t="n">
-        <v>103403</v>
+        <v>101793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223246</v>
+        <v>222929</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Backruta</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Thalictrum simplex</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Giljeskruv, Sm</t>
+          <t>Skruvagöl 450 m N, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530411</v>
+        <v>530404</v>
       </c>
       <c r="R9" t="n">
-        <v>6306455</v>
+        <v>6306428</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,12 +1565,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1983-12-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F1g 3213. SOM: Thalictrum simplex. LEG: Bengt-Erik Eriksson. KOM: Det. ThK</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,69 +1584,69 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Åkerkant</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Backman</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88236870</t>
+          <t>https://artportalen.se/Sighting/75062708</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88236890</v>
+        <v>88236870</v>
       </c>
       <c r="B10" t="n">
-        <v>104641</v>
+        <v>103403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224416</v>
+        <v>223246</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1711,13 +1717,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88236890</t>
+          <t>https://artportalen.se/Sighting/88236870</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74462643</v>
+        <v>88236890</v>
       </c>
       <c r="B11" t="n">
         <v>104641</v>
@@ -1728,37 +1734,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224417</v>
+        <v>224416</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk solvända</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. obscurum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Celak.) Holub</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>21 Pkt 230 1000 m NV, Sm</t>
+          <t>Giljeskruv, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530404</v>
+        <v>530411</v>
       </c>
       <c r="R11" t="n">
-        <v>6306428</v>
+        <v>6306455</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1782,17 +1800,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3213. SOM: Helianthemum nummularium ssp. obscurum. LEG: Bengt-Erik Eriksson, Göran Wendt</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,42 +1814,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Ängsmark-vägren</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74462643</t>
+          <t>https://artportalen.se/Sighting/88236890</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95063139</v>
+        <v>74462643</v>
       </c>
       <c r="B12" t="n">
-        <v>5394</v>
+        <v>104641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,58 +1849,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101199</v>
+        <v>224417</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hårig blombock</t>
+          <t>Mörk solvända</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Etorofus pubescens</t>
+          <t>Helianthemum nummularium subsp. obscurum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Celak.) Holub</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vändplatsen öster om St. Kättlagöl, Sm</t>
+          <t>21 Pkt 230 1000 m NV, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529607</v>
+        <v>530404</v>
       </c>
       <c r="R12" t="n">
-        <v>6305681</v>
+        <v>6306428</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,17 +1903,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>1991-12-31</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mycket äldre tallar på den sidan gölen, men området är klart påverkat av skogsbruk.</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3213. SOM: Helianthemum nummularium ssp. obscurum. LEG: Bengt-Erik Eriksson, Göran Wendt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,88 +1922,101 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Ängsmark-vägren</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Jönsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Jönsson, Mikael Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95063139</t>
+          <t>https://artportalen.se/Sighting/74462643</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118843856</v>
+        <v>95063139</v>
       </c>
       <c r="B13" t="n">
-        <v>58439</v>
+        <v>5394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>101199</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Hårig blombock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Etorofus pubescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vändplanen Kättlagöl, Sm</t>
+          <t>Vändplatsen öster om St. Kättlagöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529609</v>
+        <v>529607</v>
       </c>
       <c r="R13" t="n">
-        <v>6305682</v>
+        <v>6305681</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2043,12 +2040,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket äldre tallar på den sidan gölen, men området är klart påverkat av skogsbruk.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,71 +2059,88 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mikael Persson</t>
+          <t>Roger Jönsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Persson, Roger Jönsson</t>
+          <t>Roger Jönsson, Mikael Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118843856</t>
+          <t>https://artportalen.se/Sighting/95063139</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>172382</v>
+        <v>118843856</v>
       </c>
       <c r="B14" t="n">
-        <v>107569</v>
+        <v>58439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>626</v>
+        <v>103018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ljungögontröst</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Euphrasia micrantha</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rchb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Giljeskruv (Skruvagöl 1000 m NV), Sm</t>
+          <t>Vändplanen Kättlagöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529607</v>
+        <v>529609</v>
       </c>
       <c r="R14" t="n">
-        <v>6306623</v>
+        <v>6305682</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2143,24 +2162,14 @@
           <t>Lenhovda</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>G-Upp-0048</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Observatör: Bengt-Erik Eriksson</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,45 +2181,30 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Skogsväg vändplats</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>G-län Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>G-län Floraväktarna</t>
+          <t>Mikael Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via G-län Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Mikael Persson, Roger Jönsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/172382</t>
+          <t>https://artportalen.se/Sighting/118843856</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>74324259</v>
+        <v>172382</v>
       </c>
       <c r="B15" t="n">
-        <v>107568</v>
+        <v>107569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,17 +2232,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skruvagöl 1000 m NV, Sm</t>
+          <t>Giljeskruv (Skruvagöl 1000 m NV), Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529602</v>
+        <v>529607</v>
       </c>
       <c r="R15" t="n">
-        <v>6306618</v>
+        <v>6306623</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2270,6 +2264,11 @@
           <t>Lenhovda</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>G-Upp-0048</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>1983-01-01</t>
@@ -2282,7 +2281,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3405. SOM: Euphrasia micrantha. LEG: Bengt-Erik Eriksson. KOM: Det. ThK</t>
+          <t>Observatör: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,82 +2295,81 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Skogsväg, vändplats</t>
-        </is>
-      </c>
+          <t>Skogsväg vändplats</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>G-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>G-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Via G-län Floraväktarna</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74324259</t>
+          <t>https://artportalen.se/Sighting/172382</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102543627</v>
+        <v>74324259</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>107568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>626</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ljungögontröst</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Euphrasia micrantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+          <t>Rchb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hygget V. Tvärskogsmaden, Sm</t>
+          <t>Skruvagöl 1000 m NV, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528184</v>
+        <v>529602</v>
       </c>
       <c r="R16" t="n">
-        <v>6305774</v>
+        <v>6306618</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2395,12 +2393,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
+          <t>1983-12-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F1g 3405. SOM: Euphrasia micrantha. LEG: Bengt-Erik Eriksson. KOM: Det. ThK</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,31 +2414,40 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Skogsväg, vändplats</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Sandström</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Sandström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102543627</t>
+          <t>https://artportalen.se/Sighting/74324259</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102539432</v>
+        <v>102543627</v>
       </c>
       <c r="B17" t="n">
-        <v>57754</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,21 +2455,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2467,12 +2479,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hygget V. Tvärskogsmaden, Sm</t>
@@ -2509,22 +2516,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2550,54 +2547,66 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102539432</t>
+          <t>https://artportalen.se/Sighting/102543627</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73982977</v>
+        <v>102539432</v>
       </c>
       <c r="B18" t="n">
-        <v>107907</v>
+        <v>57754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219955</v>
+        <v>102118</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 Pkt 235.4 1500 m SV Giljeskruvsområdet, Sm</t>
+          <t>Hygget V. Tvärskogsmaden, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530306</v>
+        <v>528184</v>
       </c>
       <c r="R18" t="n">
-        <v>6306227</v>
+        <v>6305774</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2621,17 +2630,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Arnica montana. LEG: Bengt-Erik Eriksson</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,48 +2660,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Johan Sandström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Johan Sandström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73982977</t>
+          <t>https://artportalen.se/Sighting/102539432</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>73983483</v>
+        <v>73982977</v>
       </c>
       <c r="B19" t="n">
-        <v>109814</v>
+        <v>107907</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220204</v>
+        <v>219955</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2742,7 +2752,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Hypochoeris maculata. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Arnica montana. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,16 +2782,16 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73983483</t>
+          <t>https://artportalen.se/Sighting/73982977</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>74965803</v>
+        <v>73983483</v>
       </c>
       <c r="B20" t="n">
-        <v>110077</v>
+        <v>109814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,16 +2799,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>220204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2853,7 +2863,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Scorzonera humilis. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Hypochoeris maculata. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,33 +2893,33 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74965803</t>
+          <t>https://artportalen.se/Sighting/73983483</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>74844478</v>
+        <v>74965803</v>
       </c>
       <c r="B21" t="n">
-        <v>106155</v>
+        <v>110077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221141</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2964,7 +2974,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Primula veris. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Scorzonera humilis. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,16 +3004,16 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74844478</t>
+          <t>https://artportalen.se/Sighting/74965803</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>74857363</v>
+        <v>74844478</v>
       </c>
       <c r="B22" t="n">
-        <v>106243</v>
+        <v>106155</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,21 +3021,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>221141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,7 +3085,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Pyrola chlorantha. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Primula veris. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3105,38 +3115,38 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74857363</t>
+          <t>https://artportalen.se/Sighting/74844478</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>75151735</v>
+        <v>74857363</v>
       </c>
       <c r="B23" t="n">
-        <v>102418</v>
+        <v>106243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221317</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3186,7 +3196,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Trifolium aureum. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Pyrola chlorantha. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,38 +3226,38 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75151735</t>
+          <t>https://artportalen.se/Sighting/74857363</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>75016623</v>
+        <v>75151735</v>
       </c>
       <c r="B24" t="n">
-        <v>103682</v>
+        <v>102418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222002</v>
+        <v>221317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3297,7 +3307,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Viola mirabilis. LEG: Bengt-Erik Eriksson, Ingvar Christoffersson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Trifolium aureum. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,38 +3337,38 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75016623</t>
+          <t>https://artportalen.se/Sighting/75151735</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>74209281</v>
+        <v>75016623</v>
       </c>
       <c r="B25" t="n">
-        <v>99754</v>
+        <v>103682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222295</v>
+        <v>222002</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3408,7 +3418,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Carex caryophyllea. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Viola mirabilis. LEG: Bengt-Erik Eriksson, Ingvar Christoffersson</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,16 +3448,16 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74209281</t>
+          <t>https://artportalen.se/Sighting/75016623</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>74247224</v>
+        <v>74209281</v>
       </c>
       <c r="B26" t="n">
-        <v>99781</v>
+        <v>99754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3455,21 +3465,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222309</v>
+        <v>222295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3519,7 +3529,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Carex ericetorum. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Carex caryophyllea. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3549,38 +3559,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74247224</t>
+          <t>https://artportalen.se/Sighting/74209281</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>74471039</v>
+        <v>74247224</v>
       </c>
       <c r="B27" t="n">
-        <v>101325</v>
+        <v>99781</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>222309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3630,7 +3640,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Hepatica nobilis. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Carex ericetorum. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3660,38 +3670,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74471039</t>
+          <t>https://artportalen.se/Sighting/74247224</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>74532081</v>
+        <v>74471039</v>
       </c>
       <c r="B28" t="n">
-        <v>99646</v>
+        <v>101325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222541</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3741,7 +3751,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Juncus squarrosus. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Hepatica nobilis. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3771,38 +3781,38 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74532081</t>
+          <t>https://artportalen.se/Sighting/74471039</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>75174542</v>
+        <v>74532081</v>
       </c>
       <c r="B29" t="n">
-        <v>103402</v>
+        <v>99646</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223246</v>
+        <v>222541</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Juncus squarrosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3852,7 +3862,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Ulmus glabra. LEG: Bengt-Erik Eriksson</t>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Juncus squarrosus. LEG: Bengt-Erik Eriksson</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3881,6 +3891,117 @@
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74532081</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>75174542</v>
+      </c>
+      <c r="B30" t="n">
+        <v>103402</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1 Pkt 235.4 1500 m SV Giljeskruvsområdet, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>530306</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6306227</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lenhovda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1983-12-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F1g 3012. SOM: Ulmus glabra. LEG: Bengt-Erik Eriksson</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/75174542</t>
         </is>
@@ -3916,6 +4037,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 987-2022 artfynd.xlsx
+++ b/artfynd/S 987-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855635</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 987-2022 artfynd.xlsx
+++ b/artfynd/S 987-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855635</v>
       </c>
       <c r="B2" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 987-2022 artfynd.xlsx
+++ b/artfynd/S 987-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855635</v>
       </c>
       <c r="B2" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 987-2022 artfynd.xlsx
+++ b/artfynd/S 987-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855635</v>
       </c>
       <c r="B2" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 987-2022 artfynd.xlsx
+++ b/artfynd/S 987-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855635</v>
       </c>
       <c r="B2" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 987-2022 artfynd.xlsx
+++ b/artfynd/S 987-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135855635</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
